--- a/Data_clean/MCAS/Estados_US/Edos_USA_2019/NORTH_DAKOTA_2019.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2019/NORTH_DAKOTA_2019.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D121"/>
+  <dimension ref="A1:D115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Calvillo</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Total</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Total</t>
@@ -503,7 +528,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Comitán de Domínguez</t>
+          <t>Comitán De Domínguez</t>
         </is>
       </c>
       <c r="C10">
@@ -514,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Total</t>
@@ -545,9 +575,14 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hidalgo del Parral</t>
+          <t>Hidalgo Del Parral</t>
         </is>
       </c>
       <c r="C13">
@@ -558,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Total</t>
@@ -589,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Monclova</t>
@@ -602,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Saltillo</t>
@@ -615,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Total</t>
@@ -630,7 +685,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -646,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -659,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -672,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -685,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -698,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Tláhuac</t>
@@ -711,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -724,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Total</t>
@@ -755,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -768,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Mezquital</t>
@@ -781,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Rodeo</t>
@@ -794,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Total</t>
@@ -809,7 +919,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -825,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -838,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Temascalapa</t>
@@ -851,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Texcoco</t>
@@ -864,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Total</t>
@@ -884,7 +1014,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Apaseo el Alto</t>
+          <t>Apaseo El Alto</t>
         </is>
       </c>
       <c r="C37">
@@ -895,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -908,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Guanajuato</t>
@@ -921,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -934,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>León</t>
@@ -947,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -960,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Romita</t>
@@ -973,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Salamanca</t>
@@ -986,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1017,9 +1187,14 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Coyuca de Benítez</t>
+          <t>Coyuca De Benítez</t>
         </is>
       </c>
       <c r="C47">
@@ -1030,9 +1205,14 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cuetzala del Progreso</t>
+          <t>Cuetzala Del Progreso</t>
         </is>
       </c>
       <c r="C48">
@@ -1043,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Leonardo Bravo</t>
@@ -1056,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Zirándaro</t>
@@ -1069,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1100,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Degollado</t>
@@ -1113,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -1126,9 +1331,14 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ixtlahuacán de los Membrillos</t>
+          <t>Ixtlahuacán De Los Membrillos</t>
         </is>
       </c>
       <c r="C55">
@@ -1139,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Jamay</t>
@@ -1152,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>San Julián</t>
@@ -1165,9 +1385,14 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tlajomulco de Zúñiga</t>
+          <t>Tlajomulco De Zúñiga</t>
         </is>
       </c>
       <c r="C58">
@@ -1178,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>San Pedro Tlaquepaque</t>
@@ -1191,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -1204,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Villa Hidalgo</t>
@@ -1217,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1248,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Apatzingán</t>
@@ -1261,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Buenavista</t>
@@ -1274,9 +1529,14 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Coalcomán de Vázquez Pallares</t>
+          <t>Coalcomán De Vázquez Pallares</t>
         </is>
       </c>
       <c r="C66">
@@ -1287,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Contepec</t>
@@ -1300,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Uruapan</t>
@@ -1313,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Yurécuaro</t>
@@ -1326,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1357,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Santiago Ixcuintla</t>
@@ -1370,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -1383,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1414,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Los Aldamas</t>
@@ -1427,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Monterrey</t>
@@ -1440,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1471,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>San Antonino Monte Verde</t>
@@ -1484,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>San Francisco Cahuacuá</t>
@@ -1497,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>San Juan Teposcolula</t>
@@ -1510,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>San Pedro Mixtepec - Distr. 22 -</t>
@@ -1523,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Santa María Atzompa</t>
@@ -1536,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Santa María Colotepec</t>
@@ -1549,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Santiago Pinotepa Nacional</t>
@@ -1562,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1593,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -1606,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1626,7 +1986,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>San Juan del Río</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C91">
@@ -1637,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1668,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Othón P. Blanco</t>
@@ -1681,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1712,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1743,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Salvador Alvarado</t>
@@ -1756,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1787,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Hermosillo</t>
@@ -1800,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Santa Ana</t>
@@ -1813,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1844,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Reynosa</t>
@@ -1857,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1888,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Minatitlán</t>
@@ -1901,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Tecolutla</t>
@@ -1914,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -1927,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1958,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1981,41 +2421,6 @@
       </c>
       <c r="D115">
         <v>1</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 800,811</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Abril de 2020</t>
-        </is>
       </c>
     </row>
   </sheetData>
